--- a/自己的/全树种树场、树叶机-作者：碳基坤/效率和骨粉消耗.xlsx
+++ b/自己的/全树种树场、树叶机-作者：碳基坤/效率和骨粉消耗.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MC\.minecraft\versions\1.21.11-Fabric_0.19.2\schematics\自己的\全树种树场、树叶机-作者：碳基坤\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD166655-161E-432A-B8FC-F49E2792C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CD6D0-4219-4513-8A0F-A7F6BCC2A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,7 +225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -427,57 +427,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -540,11 +496,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -582,74 +556,77 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,13 +918,13 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="16" style="26" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" style="26" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="26"/>
+    <col min="1" max="1" width="22.44140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16" style="14" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
@@ -977,7 +954,7 @@
       <c r="B2" s="5">
         <v>8.6</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="18">
         <f xml:space="preserve"> -INT(-B2/5.4)</f>
         <v>2</v>
       </c>
@@ -994,13 +971,13 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="61.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="8">
         <v>7.1</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="18">
         <f t="shared" ref="C3:C21" si="0" xml:space="preserve"> -INT(-B3/5.4)</f>
         <v>2</v>
       </c>
@@ -1023,7 +1000,7 @@
       <c r="B4" s="8">
         <v>10.4</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1046,7 +1023,7 @@
       <c r="B5" s="8">
         <v>12.8</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1069,7 +1046,7 @@
       <c r="B6" s="8">
         <v>8.9</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1092,7 +1069,7 @@
       <c r="B7" s="8">
         <v>8.6999999999999993</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1115,7 +1092,7 @@
       <c r="B8" s="11">
         <v>7.2</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1138,7 +1115,7 @@
       <c r="B9" s="5">
         <v>17.655080000000002</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1161,7 +1138,7 @@
       <c r="B10" s="11">
         <v>17.602879999999999</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="16">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1184,18 +1161,18 @@
       <c r="B11" s="5">
         <v>8.7899999999999991</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="31">
         <v>8.6053999999999995</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="31">
         <f t="shared" si="1"/>
         <v>0.95615555555555554</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="29">
         <f t="shared" si="2"/>
         <v>5.5333076131687235</v>
       </c>
@@ -1207,13 +1184,13 @@
       <c r="B12" s="11">
         <v>4.63</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1222,7 +1199,7 @@
       <c r="B13" s="2">
         <v>12.401109999999999</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1245,15 +1222,15 @@
       <c r="B14" s="5">
         <v>1.7169000000000001</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29"/>
     </row>
     <row r="15" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -1262,13 +1239,13 @@
       <c r="B15" s="8">
         <v>1.3684000000000001</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
     </row>
     <row r="16" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1277,13 +1254,13 @@
       <c r="B16" s="8">
         <v>1.3684000000000001</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
     </row>
     <row r="17" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -1292,13 +1269,13 @@
       <c r="B17" s="8">
         <v>1.6918</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
@@ -1307,13 +1284,13 @@
       <c r="B18" s="8">
         <v>2.0158999999999998</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
     </row>
     <row r="19" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
@@ -1322,13 +1299,13 @@
       <c r="B19" s="8">
         <v>1.5875999999999999</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -1337,95 +1314,98 @@
       <c r="B20" s="8">
         <v>1.0758000000000001</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15">
         <v>1.4073</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="21">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="5">
         <v>1.5502</v>
       </c>
-      <c r="C22" s="32">
-        <f xml:space="preserve"> -INT(-B2/5.4)</f>
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="19">
+        <f xml:space="preserve"> -INT(-B22/5.4)</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="31">
         <v>1.1196999999999999</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="31">
         <f>D22/9</f>
         <v>0.1244111111111111</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="29">
         <f>E22*10000/1728</f>
         <v>0.71997170781893005</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28"/>
+      <c r="B23" s="11">
+        <v>1.5502</v>
+      </c>
+      <c r="C23" s="22">
+        <f xml:space="preserve"> -INT(-B23/5.4)</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="30"/>
     </row>
     <row r="24" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
+  <mergeCells count="9">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="C22:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="D14:F21"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
